--- a/tutor_forms/016_peer_tutoring_program_impact_assessment--tutor_forms.xlsx
+++ b/tutor_forms/016_peer_tutoring_program_impact_assessment--tutor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_1</t>
+          <t>program_purpose</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What is the purpose of the peer tutoring program in your school?</t>
+          <t>What is the purpose of the peer tutoring program?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_2</t>
+          <t>meeting_frequency</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_3</t>
+          <t>session_duration</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -577,7 +577,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_4</t>
+          <t>primary_goal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_5</t>
+          <t>secondary_goals</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Select the secondary goal of the peer tutoring program</t>
+          <t>Select the secondary goals of the peer tutoring program</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_6</t>
+          <t>session_time</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -646,7 +646,7 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_7</t>
+          <t>communication_methods</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_8</t>
+          <t>data_collection</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What is the average number of sessions per week?</t>
+          <t>What is the method of data collection for the peer tutoring program?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_9</t>
+          <t>meeting_frequency_staff</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>How many students are in the peer tutoring program?</t>
+          <t>How often do staff members meet with students?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,23 +722,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_10</t>
+          <t>student_group_size</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What is the average time of day for sessions?</t>
+          <t>What is the average number of students in each group?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_11</t>
+          <t>staff_meeting_frequency</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What is the method of data collection for the peer tutoring program?</t>
+          <t>How often do staff members meet with each other?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,40 +768,40 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_12</t>
+          <t>staff_meeting_time</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>How often do program staff meet with students?</t>
+          <t>What is the average time of day for staff meetings?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_13</t>
+          <t>student_meeting_frequency</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>How many students are in the peer tutoring program?</t>
+          <t>How often do students meet with each other?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_14</t>
+          <t>communication_staff</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>What is the average number of students per group?</t>
+          <t>What is the primary method of communication with staff members?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,40 +837,40 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_15</t>
+          <t>session_time_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>How often do staff members meet with students?</t>
+          <t>What is the average time of day for sessions?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_16</t>
+          <t>data_collection_staff</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>What is the average time of day for sessions?</t>
+          <t>What is the method of data collection for staff members?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_17</t>
+          <t>staff_meeting_frequency_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>What is the method of data collection for the peer tutoring program?</t>
+          <t>Staff Meeting Frequency 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_18</t>
+          <t>student_meeting_frequency_staff</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -934,156 +934,41 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_19</t>
+          <t>group_size</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>What is the average number of students in each group?</t>
+          <t>Group Size</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_20</t>
+          <t>meeting_time</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>What is the primary method of communication with staff members?</t>
+          <t>What is the average time of day for staff-student meetings?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>peer_tutoring_program_impact_assessment_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>What is the average time of day for staff meetings?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>peer_tutoring_program_impact_assessment_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>What is the method of data collection for staff members?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>peer_tutoring_program_impact_assessment_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>How often do staff members meet with students?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>peer_tutoring_program_impact_assessment_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>What is the average time of day for staff-student meetings?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>peer_tutoring_program_impact_assessment_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>How often do students meet with staff members?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +983,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,612 +1011,561 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_4_choices</t>
+          <t>primary_goal_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>improve_academic_performance</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Improve academic performance</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_4_choices</t>
+          <t>primary_goal_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>enhance_social_skills</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Enhance social skills</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_4_choices</t>
+          <t>primary_goal_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>increase_student_engagement</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Increase student engagement</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_5_choices</t>
+          <t>secondary_goals_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>improve_academic_performance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Improve academic performance</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_5_choices</t>
+          <t>secondary_goals_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>enhance_social_skills</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Enhance social skills</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_5_choices</t>
+          <t>secondary_goals_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>increase_student_engagement</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Increase student engagement</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_7_choices</t>
+          <t>communication_methods_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_7_choices</t>
+          <t>communication_methods_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_7_choices</t>
+          <t>communication_methods_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_11_choices</t>
+          <t>data_collection_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>surveys</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Surveys</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_11_choices</t>
+          <t>data_collection_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>observations</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Observations</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_11_choices</t>
+          <t>data_collection_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>interviews</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Interviews</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_12_choices</t>
+          <t>meeting_frequency_staff_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_12_choices</t>
+          <t>meeting_frequency_staff_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_12_choices</t>
+          <t>meeting_frequency_staff_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_15_choices</t>
+          <t>staff_meeting_frequency_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_15_choices</t>
+          <t>staff_meeting_frequency_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_15_choices</t>
+          <t>staff_meeting_frequency_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_17_choices</t>
+          <t>student_meeting_frequency_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_17_choices</t>
+          <t>student_meeting_frequency_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_17_choices</t>
+          <t>student_meeting_frequency_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_18_choices</t>
+          <t>communication_staff_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_18_choices</t>
+          <t>communication_staff_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_18_choices</t>
+          <t>communication_staff_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_20_choices</t>
+          <t>data_collection_staff_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>surveys</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Surveys</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_20_choices</t>
+          <t>data_collection_staff_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>observations</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Observations</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_20_choices</t>
+          <t>data_collection_staff_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>interviews</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Interviews</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_22_choices</t>
+          <t>staff_meeting_frequency_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_22_choices</t>
+          <t>staff_meeting_frequency_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_22_choices</t>
+          <t>staff_meeting_frequency_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_23_choices</t>
+          <t>student_meeting_frequency_staff_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_23_choices</t>
+          <t>student_meeting_frequency_staff_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>peer_tutoring_program_impact_assessment_23_choices</t>
+          <t>student_meeting_frequency_staff_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>peer_tutoring_program_impact_assessment_25_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>peer_tutoring_program_impact_assessment_25_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>peer_tutoring_program_impact_assessment_25_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Option 3</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
